--- a/03_Outputs/all/01_TablasDescriptivas/idx11_pobreza_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx11_pobreza_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>13.02998061653005</v>
+        <v>13.02998061653008</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>3.084005647723399</v>
+        <v>3.084005647723415</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>2.097298262183471</v>
+        <v>2.097298262183465</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.084397297338372</v>
+        <v>1.084397297338374</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.3191938316400754</v>
+        <v>0.3191938316400745</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.2093037432301206</v>
+        <v>0.2093037432301205</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.1448180867396709</v>
+        <v>0.1448180867396705</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.0664440663603508</v>
+        <v>0.06644406636035091</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.06215472769245324</v>
+        <v>0.06215472769245341</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.04918721588746891</v>
+        <v>0.04918721588746879</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.03956448776030679</v>
+        <v>0.03956448776030676</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.03342158737464059</v>
+        <v>0.03342158737464055</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.02383642364297956</v>
+        <v>0.02383642364297957</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.000377486664567977</v>
+        <v>0.0003774866645679805</v>
       </c>
       <c r="C18">
         <v>17</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.000128935934892951</v>
+        <v>0.0001289359348929539</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>7.801768797992509E-05</v>
+        <v>7.801768797992246E-05</v>
       </c>
       <c r="C20">
         <v>19</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>3.570248226711806E-05</v>
+        <v>3.570248226711844E-05</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>2.614577076082099E-15</v>
+        <v>2.614577084930187E-15</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>2.099552969152432E-15</v>
+        <v>2.099552963972423E-15</v>
       </c>
       <c r="C23">
         <v>22</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.76125944894973E-15</v>
+        <v>1.761259455150306E-15</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>13.02998061653005</v>
+        <v>13.02998061653008</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>16.11398626425345</v>
+        <v>16.11398626425349</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>18.21128452643692</v>
+        <v>18.21128452643696</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>20.17611401290438</v>
+        <v>20.17611401290442</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>21.26051131024276</v>
+        <v>21.26051131024279</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>21.91901325549123</v>
+        <v>21.91901325549127</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>22.2382070871313</v>
+        <v>22.23820708713134</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>22.44751083036142</v>
+        <v>22.44751083036146</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>22.5923289171011</v>
+        <v>22.59232891710113</v>
       </c>
       <c r="C33">
         <v>9</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>22.72477134851207</v>
+        <v>22.72477134851211</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>22.79121541487243</v>
+        <v>22.79121541487246</v>
       </c>
       <c r="C35">
         <v>11</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>22.85337014256488</v>
+        <v>22.85337014256492</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>22.90255735845234</v>
+        <v>22.90255735845239</v>
       </c>
       <c r="C37">
         <v>13</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>22.94212184621265</v>
+        <v>22.94212184621269</v>
       </c>
       <c r="C38">
         <v>14</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>22.97554343358729</v>
+        <v>22.97554343358733</v>
       </c>
       <c r="C39">
         <v>15</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>22.99937985723027</v>
+        <v>22.99937985723031</v>
       </c>
       <c r="C40">
         <v>16</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>22.99975734389484</v>
+        <v>22.99975734389488</v>
       </c>
       <c r="C41">
         <v>17</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>22.99988627982973</v>
+        <v>22.99988627982977</v>
       </c>
       <c r="C42">
         <v>18</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>22.99996429751771</v>
+        <v>22.99996429751775</v>
       </c>
       <c r="C43">
         <v>19</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>22.99999999999998</v>
+        <v>23.00000000000002</v>
       </c>
       <c r="C44">
         <v>20</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>22.99999999999998</v>
+        <v>23.00000000000002</v>
       </c>
       <c r="C45">
         <v>21</v>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>22.99999999999999</v>
+        <v>23.00000000000002</v>
       </c>
       <c r="C46">
         <v>22</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>22.99999999999999</v>
+        <v>23.00000000000003</v>
       </c>
       <c r="C47">
         <v>23</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="B48">
-        <v>56.65208963708722</v>
+        <v>56.65208963708723</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B49">
-        <v>13.40872020749305</v>
+        <v>13.40872020749309</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>9.118688096449882</v>
+        <v>9.118688096449839</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>8.542736897684611</v>
+        <v>8.542736897684593</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="B52">
-        <v>4.714770857992924</v>
+        <v>4.714770857992927</v>
       </c>
       <c r="C52">
         <v>5</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>2.863051935862939</v>
+        <v>2.863051935862934</v>
       </c>
       <c r="C53">
         <v>6</v>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>1.387799268000329</v>
+        <v>1.387799268000322</v>
       </c>
       <c r="C54">
         <v>7</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.9100162749135686</v>
+        <v>0.9100162749135662</v>
       </c>
       <c r="C55">
         <v>8</v>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.629643855389874</v>
+        <v>0.629643855389871</v>
       </c>
       <c r="C56">
         <v>9</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.5758366583086073</v>
+        <v>0.5758366583086063</v>
       </c>
       <c r="C57">
         <v>10</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.2702379464889273</v>
+        <v>0.2702379464889275</v>
       </c>
       <c r="C59">
         <v>12</v>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.2138574603802997</v>
+        <v>0.2138574603802988</v>
       </c>
       <c r="C60">
         <v>13</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.172019512001334</v>
+        <v>0.1720195120013336</v>
       </c>
       <c r="C61">
         <v>14</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.1453112494549592</v>
+        <v>0.1453112494549587</v>
       </c>
       <c r="C62">
         <v>15</v>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.1036366245346938</v>
+        <v>0.1036366245346937</v>
       </c>
       <c r="C63">
         <v>16</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.001641246367686858</v>
+        <v>0.00164124636768687</v>
       </c>
       <c r="C64">
         <v>17</v>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.0005605910212737004</v>
+        <v>0.0005605910212737118</v>
       </c>
       <c r="C65">
         <v>18</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.0003392073390431528</v>
+        <v>0.0003392073390431407</v>
       </c>
       <c r="C66">
         <v>19</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.0001552281837700786</v>
+        <v>0.00015522818377008</v>
       </c>
       <c r="C67">
         <v>20</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="B68">
-        <v>1.136772641774826E-14</v>
+        <v>1.136772645621819E-14</v>
       </c>
       <c r="C68">
         <v>21</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B69">
-        <v>9.12849117022797E-15</v>
+        <v>9.128491147706177E-15</v>
       </c>
       <c r="C69">
         <v>22</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B70">
-        <v>7.657649778042312E-15</v>
+        <v>7.657649805001322E-15</v>
       </c>
       <c r="C70">
         <v>23</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>56.65208963708722</v>
+        <v>56.65208963708723</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B72">
-        <v>70.06080984458026</v>
+        <v>70.06080984458032</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>79.17949794103015</v>
+        <v>79.17949794103016</v>
       </c>
       <c r="C73">
         <v>3</v>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B75">
-        <v>92.43700569670769</v>
+        <v>92.43700569670767</v>
       </c>
       <c r="C75">
         <v>5</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B76">
-        <v>95.30005763257063</v>
+        <v>95.30005763257061</v>
       </c>
       <c r="C76">
         <v>6</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>96.68785690057095</v>
+        <v>96.68785690057094</v>
       </c>
       <c r="C77">
         <v>7</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>97.59787317548451</v>
+        <v>97.59787317548449</v>
       </c>
       <c r="C78">
         <v>8</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>98.2275170308744</v>
+        <v>98.22751703087438</v>
       </c>
       <c r="C79">
         <v>9</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B80">
-        <v>98.803353689183</v>
+        <v>98.80335368918298</v>
       </c>
       <c r="C80">
         <v>10</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B82">
-        <v>99.36247888071692</v>
+        <v>99.36247888071691</v>
       </c>
       <c r="C82">
         <v>12</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="C92">
         <v>22</v>
